--- a/salidas/empresas/HAL.xlsx
+++ b/salidas/empresas/HAL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>28.7421703338623</v>
+        <v>28.74216651916504</v>
       </c>
       <c r="C2" t="n">
         <v>39.81000137329102</v>
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>26.41705703735352</v>
+        <v>26.41704750061035</v>
       </c>
       <c r="C4" t="n">
         <v>36.5099983215332</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>28.27297019958496</v>
+        <v>28.27297592163086</v>
       </c>
       <c r="C5" t="n">
         <v>39.07500076293945</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>27.04010581970215</v>
+        <v>27.04010963439941</v>
       </c>
       <c r="C6" t="n">
         <v>37.29499816894531</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>26.90236854553223</v>
+        <v>26.90236282348633</v>
       </c>
       <c r="C7" t="n">
         <v>37.10499954223633</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>24.18710708618164</v>
+        <v>24.18711471557617</v>
       </c>
       <c r="C8" t="n">
         <v>33.36000061035156</v>
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>23.50726318359375</v>
+        <v>23.50727081298828</v>
       </c>
       <c r="C11" t="n">
         <v>32.34999847412109</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>24.57366561889648</v>
+        <v>24.57365226745605</v>
       </c>
       <c r="C12" t="n">
         <v>33.7400016784668</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>22.61447143554688</v>
+        <v>22.61446571350098</v>
       </c>
       <c r="C13" t="n">
         <v>31.04999923706055</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>21.51469802856445</v>
+        <v>21.51469993591309</v>
       </c>
       <c r="C14" t="n">
         <v>29.54000091552734</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>22.5728588104248</v>
+        <v>22.57285690307617</v>
       </c>
       <c r="C15" t="n">
         <v>30.92000007629395</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>23.17148780822754</v>
+        <v>23.17149925231934</v>
       </c>
       <c r="C16" t="n">
         <v>31.73999977111816</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>23.19339370727539</v>
+        <v>23.19339561462402</v>
       </c>
       <c r="C17" t="n">
         <v>31.77000045776367</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>26.31112480163574</v>
+        <v>26.31112098693848</v>
       </c>
       <c r="C18" t="n">
         <v>35.95000076293945</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>25.24989700317383</v>
+        <v>25.24989318847656</v>
       </c>
       <c r="C19" t="n">
         <v>34.5</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>26.36236190795898</v>
+        <v>26.36235046386719</v>
       </c>
       <c r="C20" t="n">
         <v>36.02000045776367</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>25.38509941101074</v>
+        <v>25.38510894775391</v>
       </c>
       <c r="C21" t="n">
         <v>34.59000015258789</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>28.18121719360352</v>
+        <v>28.18121337890625</v>
       </c>
       <c r="C22" t="n">
         <v>38.40000152587891</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>28.92978477478027</v>
+        <v>28.92977905273438</v>
       </c>
       <c r="C23" t="n">
         <v>39.41999816894531</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>26.93516540527344</v>
+        <v>26.93517303466797</v>
       </c>
       <c r="C24" t="n">
         <v>36.61000061035156</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>27.89162445068359</v>
+        <v>27.89163017272949</v>
       </c>
       <c r="C25" t="n">
         <v>37.90999984741211</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>24.40424156188965</v>
+        <v>24.40425300598145</v>
       </c>
       <c r="C26" t="n">
         <v>33.16999816894531</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>28.24626350402832</v>
+        <v>28.24626922607422</v>
       </c>
       <c r="C27" t="n">
         <v>38.29999923706055</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>29.00588989257812</v>
+        <v>29.00589942932129</v>
       </c>
       <c r="C28" t="n">
         <v>39.33000183105469</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>33.85863876342773</v>
+        <v>33.8586311340332</v>
       </c>
       <c r="C29" t="n">
         <v>45.90999984741211</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>35.89383697509766</v>
+        <v>35.89383316040039</v>
       </c>
       <c r="C30" t="n">
         <v>48.58000183105469</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>39.21131134033203</v>
+        <v>39.2112922668457</v>
       </c>
       <c r="C31" t="n">
         <v>53.06999969482422</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>33.11571502685547</v>
+        <v>33.11572265625</v>
       </c>
       <c r="C32" t="n">
         <v>44.81999969482422</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>32.52947235107422</v>
+        <v>32.52947616577148</v>
       </c>
       <c r="C33" t="n">
         <v>43.93999862670898</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>23.97883033752441</v>
+        <v>23.97883224487305</v>
       </c>
       <c r="C34" t="n">
         <v>32.38999938964844</v>
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>13.02955722808838</v>
+        <v>13.02956008911133</v>
       </c>
       <c r="C36" t="n">
         <v>17.60000038146973</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>13.5281229019165</v>
+        <v>13.52812004089355</v>
       </c>
       <c r="C37" t="n">
         <v>18.18000030517578</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>12.83608722686768</v>
+        <v>12.83608436584473</v>
       </c>
       <c r="C38" t="n">
         <v>17.25</v>
@@ -1185,7 +1197,7 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>11.57392597198486</v>
+        <v>11.57392501831055</v>
       </c>
       <c r="C40" t="n">
         <v>15.47000026702881</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>15.12765693664551</v>
+        <v>15.12765979766846</v>
       </c>
       <c r="C41" t="n">
         <v>20.21999931335449</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>17.22542762756348</v>
+        <v>17.22541999816895</v>
       </c>
       <c r="C42" t="n">
         <v>22.93000030517578</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>15.55021095275879</v>
+        <v>15.55020618438721</v>
       </c>
       <c r="C43" t="n">
         <v>20.70000076293945</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>16.59439659118652</v>
+        <v>16.59440040588379</v>
       </c>
       <c r="C44" t="n">
         <v>22.09000015258789</v>
@@ -1305,11 +1317,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>17.87805557250977</v>
+        <v>17.87805938720703</v>
       </c>
       <c r="C45" t="n">
         <v>23.70999908447266</v>
@@ -1330,11 +1342,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>20.44930076599121</v>
+        <v>20.44930267333984</v>
       </c>
       <c r="C46" t="n">
         <v>27.1200008392334</v>
@@ -1355,11 +1367,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>22.02522468566895</v>
+        <v>22.02522087097168</v>
       </c>
       <c r="C47" t="n">
         <v>29.20999908447266</v>
@@ -1380,11 +1392,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>22.13832473754883</v>
+        <v>22.13833045959473</v>
       </c>
       <c r="C48" t="n">
         <v>29.36000061035156</v>
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>22.75854110717773</v>
+        <v>22.75853538513184</v>
       </c>
       <c r="C49" t="n">
         <v>30.09000015258789</v>
@@ -1430,11 +1442,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>22.09294700622559</v>
+        <v>22.09294509887695</v>
       </c>
       <c r="C50" t="n">
         <v>29.20999908447266</v>
@@ -1455,11 +1467,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>22.87253379821777</v>
+        <v>22.87252807617188</v>
       </c>
       <c r="C51" t="n">
         <v>30.14999961853027</v>
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>22.85736465454102</v>
+        <v>22.85735511779785</v>
       </c>
       <c r="C52" t="n">
         <v>30.1299991607666</v>
@@ -1505,11 +1517,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>23.25184440612793</v>
+        <v>23.25183486938477</v>
       </c>
       <c r="C53" t="n">
         <v>30.64999961853027</v>
@@ -1530,11 +1542,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>18.90238380432129</v>
+        <v>18.90238189697266</v>
       </c>
       <c r="C54" t="n">
         <v>24.82999992370605</v>
@@ -1555,7 +1567,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1580,7 +1592,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1605,7 +1617,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
@@ -1630,7 +1642,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>24.3289852142334</v>
+        <v>24.3289909362793</v>
       </c>
       <c r="C59" t="n">
         <v>31.86000061035156</v>
@@ -1680,11 +1692,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>28.89543342590332</v>
+        <v>28.89544105529785</v>
       </c>
       <c r="C60" t="n">
         <v>37.84000015258789</v>
@@ -1705,11 +1717,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>31.25301742553711</v>
+        <v>31.25300407409668</v>
       </c>
       <c r="C61" t="n">
         <v>40.83000183105469</v>
@@ -1730,11 +1742,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>34.44488906860352</v>
+        <v>34.44490814208984</v>
       </c>
       <c r="C62" t="n">
         <v>45</v>
@@ -1755,11 +1767,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>35.99874114990234</v>
+        <v>35.99873733520508</v>
       </c>
       <c r="C63" t="n">
         <v>46.93999862670898</v>
@@ -1784,11 +1796,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>38.22279357910156</v>
+        <v>38.22278213500977</v>
       </c>
       <c r="C64" t="n">
         <v>49.84000015258789</v>
@@ -1813,11 +1825,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>38.71360015869141</v>
+        <v>38.7136116027832</v>
       </c>
       <c r="C65" t="n">
         <v>50.47999954223633</v>
@@ -1842,11 +1854,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>38.52898406982422</v>
+        <v>38.52896499633789</v>
       </c>
       <c r="C66" t="n">
         <v>50.15000152587891</v>
@@ -1871,11 +1883,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>39.18200302124023</v>
+        <v>39.1820068359375</v>
       </c>
       <c r="C67" t="n">
         <v>51</v>
@@ -1900,11 +1912,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>42.04768753051758</v>
+        <v>42.04766845703125</v>
       </c>
       <c r="C68" t="n">
         <v>54.72999954223633</v>
@@ -1929,7 +1941,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1958,11 +1970,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>23.49713897705078</v>
+        <v>23.49714660644531</v>
       </c>
       <c r="C70" t="n">
         <v>30.52000045776367</v>
@@ -1987,11 +1999,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>28.76321029663086</v>
+        <v>28.76321411132812</v>
       </c>
       <c r="C71" t="n">
         <v>37.36000061035156</v>
@@ -2016,7 +2028,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -2045,11 +2057,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>26.64029502868652</v>
+        <v>26.64030265808105</v>
       </c>
       <c r="C73" t="n">
         <v>34.5099983215332</v>
@@ -2074,7 +2086,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2103,11 +2115,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>28.24598503112793</v>
+        <v>28.24599266052246</v>
       </c>
       <c r="C75" t="n">
         <v>36.59000015258789</v>
@@ -2132,11 +2144,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>25.68544960021973</v>
+        <v>25.6854419708252</v>
       </c>
       <c r="C76" t="n">
         <v>33.18999862670898</v>
@@ -2161,11 +2173,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>26.48255348205566</v>
+        <v>26.48255729675293</v>
       </c>
       <c r="C77" t="n">
         <v>34.22000122070312</v>
@@ -2190,11 +2202,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>23.2631664276123</v>
+        <v>23.26317024230957</v>
       </c>
       <c r="C78" t="n">
         <v>30.05999946594238</v>
@@ -2219,11 +2231,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>22.03694534301758</v>
+        <v>22.03695487976074</v>
       </c>
       <c r="C79" t="n">
         <v>28.38999938964844</v>
@@ -2248,11 +2260,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>25.71623611450195</v>
+        <v>25.71624374389648</v>
       </c>
       <c r="C80" t="n">
         <v>33.13000106811523</v>
@@ -2277,11 +2289,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>25.49898910522461</v>
+        <v>25.49897384643555</v>
       </c>
       <c r="C81" t="n">
         <v>32.7599983215332</v>
@@ -2306,11 +2318,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>26.22285652160645</v>
+        <v>26.22286415100098</v>
       </c>
       <c r="C82" t="n">
         <v>33.68999862670898</v>
@@ -2335,11 +2347,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>25.13314819335938</v>
+        <v>25.13315582275391</v>
       </c>
       <c r="C83" t="n">
         <v>32.29000091552734</v>
@@ -2364,7 +2376,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2393,11 +2405,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>27.07487487792969</v>
+        <v>27.07487106323242</v>
       </c>
       <c r="C85" t="n">
         <v>34.68999862670898</v>
@@ -2422,11 +2434,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>31.74995422363281</v>
+        <v>31.74995994567871</v>
       </c>
       <c r="C86" t="n">
         <v>40.68000030517578</v>
@@ -2451,11 +2463,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>32.39774703979492</v>
+        <v>32.39775085449219</v>
       </c>
       <c r="C87" t="n">
         <v>41.5099983215332</v>
@@ -2480,11 +2492,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>31.63655662536621</v>
+        <v>31.63654327392578</v>
       </c>
       <c r="C88" t="n">
         <v>40.40999984741211</v>
@@ -2509,11 +2521,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>33.48418426513672</v>
+        <v>33.48416900634766</v>
       </c>
       <c r="C89" t="n">
         <v>42.77000045776367</v>
@@ -2538,7 +2550,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2567,11 +2579,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>32.75999069213867</v>
+        <v>32.7599983215332</v>
       </c>
       <c r="C91" t="n">
         <v>41.72000122070312</v>
@@ -2596,11 +2608,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>35.48476409912109</v>
+        <v>35.48475646972656</v>
       </c>
       <c r="C92" t="n">
         <v>45.18999862670898</v>
@@ -2625,11 +2637,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>37.78857421875</v>
+        <v>37.78858947753906</v>
       </c>
       <c r="C93" t="n">
         <v>48</v>
@@ -2654,11 +2666,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>37.90666580200195</v>
+        <v>37.90668106079102</v>
       </c>
       <c r="C94" t="n">
         <v>48.15000152587891</v>
@@ -2683,7 +2695,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2712,11 +2724,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>41.47296905517578</v>
+        <v>41.47296142578125</v>
       </c>
       <c r="C96" t="n">
         <v>52.68000030517578</v>
@@ -2741,11 +2753,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>40.06908798217773</v>
+        <v>40.0690803527832</v>
       </c>
       <c r="C97" t="n">
         <v>50.75</v>
@@ -2770,11 +2782,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>38.6953010559082</v>
+        <v>38.69528198242188</v>
       </c>
       <c r="C98" t="n">
         <v>49.0099983215332</v>
@@ -2799,7 +2811,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2828,7 +2840,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2857,11 +2869,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>49.92760467529297</v>
+        <v>49.9276008605957</v>
       </c>
       <c r="C101" t="n">
         <v>63.06999969482422</v>
@@ -2886,7 +2898,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2915,7 +2927,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2944,11 +2956,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>54.74102020263672</v>
+        <v>54.74101638793945</v>
       </c>
       <c r="C104" t="n">
         <v>68.98999786376953</v>
@@ -2973,11 +2985,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>53.76572418212891</v>
+        <v>53.76573944091797</v>
       </c>
       <c r="C105" t="n">
         <v>67.61000061035156</v>
@@ -3002,11 +3014,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>51.30052185058594</v>
+        <v>51.30051803588867</v>
       </c>
       <c r="C106" t="n">
         <v>64.51000213623047</v>
@@ -3031,11 +3043,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>43.84917068481445</v>
+        <v>43.84918212890625</v>
       </c>
       <c r="C107" t="n">
         <v>55.13999938964844</v>
@@ -3060,11 +3072,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>33.55886077880859</v>
+        <v>33.55885314941406</v>
       </c>
       <c r="C108" t="n">
         <v>42.20000076293945</v>
@@ -3089,11 +3101,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>31.41671562194824</v>
+        <v>31.41671943664551</v>
       </c>
       <c r="C109" t="n">
         <v>39.33000183105469</v>
@@ -3118,11 +3130,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>31.94391822814941</v>
+        <v>31.94391441345215</v>
       </c>
       <c r="C110" t="n">
         <v>39.9900016784668</v>
@@ -3147,11 +3159,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>34.30037689208984</v>
+        <v>34.30038070678711</v>
       </c>
       <c r="C111" t="n">
         <v>42.93999862670898</v>
@@ -3176,11 +3188,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>35.19878005981445</v>
+        <v>35.19879531860352</v>
       </c>
       <c r="C112" t="n">
         <v>43.88000106811523</v>
@@ -3205,11 +3217,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>39.2657470703125</v>
+        <v>39.26573944091797</v>
       </c>
       <c r="C113" t="n">
         <v>48.95000076293945</v>
@@ -3234,11 +3246,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>36.4180793762207</v>
+        <v>36.41808700561523</v>
       </c>
       <c r="C114" t="n">
         <v>45.40000152587891</v>
@@ -3263,11 +3275,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>34.68656158447266</v>
+        <v>34.68656921386719</v>
       </c>
       <c r="C115" t="n">
         <v>43.06999969482422</v>
@@ -3292,11 +3304,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>33.65571212768555</v>
+        <v>33.65571594238281</v>
       </c>
       <c r="C116" t="n">
         <v>41.79000091552734</v>
@@ -3321,11 +3333,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>31.83916091918945</v>
+        <v>31.83915710449219</v>
       </c>
       <c r="C117" t="n">
         <v>39.34999847412109</v>
@@ -3350,11 +3362,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>28.60265731811523</v>
+        <v>28.6026668548584</v>
       </c>
       <c r="C118" t="n">
         <v>35.34999847412109</v>
@@ -3379,11 +3391,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>31.05431365966797</v>
+        <v>31.05432319641113</v>
       </c>
       <c r="C119" t="n">
         <v>38.38000106811523</v>
@@ -3408,7 +3420,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3437,11 +3449,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>27.66767692565918</v>
+        <v>27.66767120361328</v>
       </c>
       <c r="C121" t="n">
         <v>34.04000091552734</v>
@@ -3466,11 +3478,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>25.83887481689453</v>
+        <v>25.8388786315918</v>
       </c>
       <c r="C122" t="n">
         <v>31.79000091552734</v>
@@ -3495,11 +3507,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>26.38187408447266</v>
+        <v>26.38188552856445</v>
       </c>
       <c r="C123" t="n">
         <v>32.27999877929688</v>
@@ -3522,11 +3534,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>29.19332695007324</v>
+        <v>29.19333457946777</v>
       </c>
       <c r="C124" t="n">
         <v>35.72000122070312</v>
@@ -3549,11 +3561,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>33.76194000244141</v>
+        <v>33.76196670532227</v>
       </c>
       <c r="C125" t="n">
         <v>41.31000137329102</v>
@@ -3576,11 +3588,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>34.61912536621094</v>
+        <v>34.61912155151367</v>
       </c>
       <c r="C126" t="n">
         <v>42.18000030517578</v>
@@ -3603,11 +3615,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>37.1716423034668</v>
+        <v>37.17164611816406</v>
       </c>
       <c r="C127" t="n">
         <v>45.29000091552734</v>
@@ -3630,11 +3642,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>35.83382034301758</v>
+        <v>35.83383178710938</v>
       </c>
       <c r="C128" t="n">
         <v>43.65999984741211</v>
@@ -3657,11 +3669,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>35.30034255981445</v>
+        <v>35.30033493041992</v>
       </c>
       <c r="C129" t="n">
         <v>43.0099983215332</v>
@@ -3684,11 +3696,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>36.98922348022461</v>
+        <v>36.98921585083008</v>
       </c>
       <c r="C130" t="n">
         <v>44.88000106811523</v>
@@ -3711,11 +3723,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>37.91231536865234</v>
+        <v>37.91230773925781</v>
       </c>
       <c r="C131" t="n">
         <v>46</v>
@@ -3738,11 +3750,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>43.7557487487793</v>
+        <v>43.75575256347656</v>
       </c>
       <c r="C132" t="n">
         <v>53.09000015258789</v>
@@ -3765,11 +3777,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>44.72854995727539</v>
+        <v>44.72855377197266</v>
       </c>
       <c r="C133" t="n">
         <v>54.09000015258789</v>
@@ -3790,7 +3802,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3815,11 +3827,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>44.35860824584961</v>
+        <v>44.35861587524414</v>
       </c>
       <c r="C135" t="n">
         <v>53.45999908447266</v>
@@ -3840,11 +3852,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>40.83215713500977</v>
+        <v>40.8321533203125</v>
       </c>
       <c r="C136" t="n">
         <v>49.20999908447266</v>
@@ -3865,11 +3877,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>38.06908798217773</v>
+        <v>38.0690803527832</v>
       </c>
       <c r="C137" t="n">
         <v>45.88000106811523</v>
@@ -3890,7 +3902,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -3915,7 +3927,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3940,11 +3952,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>35.3552131652832</v>
+        <v>35.35520553588867</v>
       </c>
       <c r="C140" t="n">
         <v>42.43999862670898</v>
@@ -3967,11 +3979,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>32.46449279785156</v>
+        <v>32.4644889831543</v>
       </c>
       <c r="C141" t="n">
         <v>38.97000122070312</v>
@@ -3994,7 +4006,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -4021,11 +4033,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>35.77035903930664</v>
+        <v>35.77035522460938</v>
       </c>
       <c r="C143" t="n">
         <v>42.7400016784668</v>
@@ -4050,11 +4062,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>34.96689987182617</v>
+        <v>34.96690368652344</v>
       </c>
       <c r="C144" t="n">
         <v>41.77999877929688</v>
@@ -4079,11 +4091,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>41.07016372680664</v>
+        <v>41.07016754150391</v>
       </c>
       <c r="C145" t="n">
         <v>48.86999893188477</v>
@@ -4108,11 +4120,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>45.1292839050293</v>
+        <v>45.12928771972656</v>
       </c>
       <c r="C146" t="n">
         <v>53.70000076293945</v>
@@ -4137,11 +4149,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>39.01119232177734</v>
+        <v>39.01119613647461</v>
       </c>
       <c r="C147" t="n">
         <v>46.41999816894531</v>
@@ -4164,11 +4176,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>39.60229873657227</v>
+        <v>39.602294921875</v>
       </c>
       <c r="C148" t="n">
         <v>46.93999862670898</v>
@@ -4191,11 +4203,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>44.70656204223633</v>
+        <v>44.70656967163086</v>
       </c>
       <c r="C149" t="n">
         <v>52.9900016784668</v>
@@ -4218,7 +4230,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4245,11 +4257,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>38.15942764282227</v>
+        <v>38.1594352722168</v>
       </c>
       <c r="C151" t="n">
         <v>45.06000137329102</v>
@@ -4272,11 +4284,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>35.92372131347656</v>
+        <v>35.92372894287109</v>
       </c>
       <c r="C152" t="n">
         <v>42.41999816894531</v>
@@ -4301,11 +4313,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>33.78117752075195</v>
+        <v>33.78116607666016</v>
       </c>
       <c r="C153" t="n">
         <v>39.88999938964844</v>
@@ -4330,7 +4342,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4359,11 +4371,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>29.50216865539551</v>
+        <v>29.50217819213867</v>
       </c>
       <c r="C155" t="n">
         <v>34.68000030517578</v>
@@ -4388,7 +4400,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4417,11 +4429,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>22.74172019958496</v>
+        <v>22.74172782897949</v>
       </c>
       <c r="C157" t="n">
         <v>26.57999992370605</v>
@@ -4446,11 +4458,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>26.83146858215332</v>
+        <v>26.83147811889648</v>
       </c>
       <c r="C158" t="n">
         <v>31.36000061035156</v>
@@ -4475,11 +4487,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>26.25821876525879</v>
+        <v>26.25822448730469</v>
       </c>
       <c r="C159" t="n">
         <v>30.69000053405762</v>
@@ -4504,11 +4516,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>25.2154483795166</v>
+        <v>25.21544647216797</v>
       </c>
       <c r="C160" t="n">
         <v>29.29999923706055</v>
@@ -4533,11 +4545,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>24.38067054748535</v>
+        <v>24.38066673278809</v>
       </c>
       <c r="C161" t="n">
         <v>28.32999992370605</v>
@@ -4562,11 +4574,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>18.32208061218262</v>
+        <v>18.32207870483398</v>
       </c>
       <c r="C162" t="n">
         <v>21.29000091552734</v>
@@ -4591,11 +4603,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>19.73439598083496</v>
+        <v>19.7343921661377</v>
       </c>
       <c r="C163" t="n">
         <v>22.73999977111816</v>
@@ -4620,11 +4632,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>19.96003150939941</v>
+        <v>19.96002578735352</v>
       </c>
       <c r="C164" t="n">
         <v>23</v>
@@ -4649,11 +4661,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>16.34986686706543</v>
+        <v>16.3498649597168</v>
       </c>
       <c r="C165" t="n">
         <v>18.84000015258789</v>
@@ -4678,11 +4690,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>16.5163516998291</v>
+        <v>16.51634407043457</v>
       </c>
       <c r="C166" t="n">
         <v>18.85000038146973</v>
@@ -4707,11 +4719,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>16.8668270111084</v>
+        <v>16.86682891845703</v>
       </c>
       <c r="C167" t="n">
         <v>19.25</v>
@@ -4736,11 +4748,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>18.39141082763672</v>
+        <v>18.39141464233398</v>
       </c>
       <c r="C168" t="n">
         <v>20.98999977111816</v>
@@ -4765,11 +4777,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>21.62784194946289</v>
+        <v>21.62783813476562</v>
       </c>
       <c r="C169" t="n">
         <v>24.46999931335449</v>
@@ -4794,7 +4806,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4823,7 +4835,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4850,11 +4862,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>6.118335247039795</v>
+        <v>6.118336200714111</v>
       </c>
       <c r="C172" t="n">
         <v>6.849999904632568</v>
@@ -4877,11 +4889,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>9.378469467163086</v>
+        <v>9.378471374511719</v>
       </c>
       <c r="C173" t="n">
         <v>10.5</v>
@@ -4904,11 +4916,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>10.49495506286621</v>
+        <v>10.49495124816895</v>
       </c>
       <c r="C174" t="n">
         <v>11.75</v>
@@ -4931,11 +4943,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>11.63706874847412</v>
+        <v>11.63706970214844</v>
       </c>
       <c r="C175" t="n">
         <v>12.97999954223633</v>
@@ -4958,11 +4970,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>12.84739780426025</v>
+        <v>12.84739589691162</v>
       </c>
       <c r="C176" t="n">
         <v>14.32999992370605</v>
@@ -4985,7 +4997,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5012,11 +5024,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>10.83341884613037</v>
+        <v>10.833420753479</v>
       </c>
       <c r="C178" t="n">
         <v>12.05000019073486</v>
@@ -5039,11 +5051,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>10.84241008758545</v>
+        <v>10.8424129486084</v>
       </c>
       <c r="C179" t="n">
         <v>12.0600004196167</v>
@@ -5066,11 +5078,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>14.91505432128906</v>
+        <v>14.91505908966064</v>
       </c>
       <c r="C180" t="n">
         <v>16.59000015258789</v>
@@ -5093,11 +5105,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>17.03672218322754</v>
+        <v>17.0367259979248</v>
       </c>
       <c r="C181" t="n">
         <v>18.89999961853027</v>
@@ -5120,11 +5132,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>15.89192771911621</v>
+        <v>15.89192390441895</v>
       </c>
       <c r="C182" t="n">
         <v>17.6299991607666</v>
@@ -5147,11 +5159,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>19.67786598205566</v>
+        <v>19.67786026000977</v>
       </c>
       <c r="C183" t="n">
         <v>21.82999992370605</v>
@@ -5174,11 +5186,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>19.38224411010742</v>
+        <v>19.38224601745605</v>
       </c>
       <c r="C184" t="n">
         <v>21.45999908447266</v>
@@ -5201,11 +5213,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>17.66619873046875</v>
+        <v>17.66620445251465</v>
       </c>
       <c r="C185" t="n">
         <v>19.55999946594238</v>
@@ -5228,11 +5240,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>20.27639770507812</v>
+        <v>20.27639389038086</v>
       </c>
       <c r="C186" t="n">
         <v>22.45000076293945</v>
@@ -5255,11 +5267,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>20.92346572875977</v>
+        <v>20.92346954345703</v>
       </c>
       <c r="C187" t="n">
         <v>23.1200008392334</v>
@@ -5282,7 +5294,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5309,11 +5321,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>18.12223243713379</v>
+        <v>18.12223434448242</v>
       </c>
       <c r="C189" t="n">
         <v>19.97999954223633</v>
@@ -5336,7 +5348,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5363,11 +5375,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>22.66639709472656</v>
+        <v>22.66640090942383</v>
       </c>
       <c r="C191" t="n">
         <v>24.98999977111816</v>
@@ -5390,11 +5402,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>19.5825366973877</v>
+        <v>19.58253479003906</v>
       </c>
       <c r="C192" t="n">
         <v>21.59000015258789</v>
@@ -5417,11 +5429,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>20.78349304199219</v>
+        <v>20.78348731994629</v>
       </c>
       <c r="C193" t="n">
         <v>22.8700008392334</v>
@@ -5442,11 +5454,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>27.93548011779785</v>
+        <v>27.93547821044922</v>
       </c>
       <c r="C194" t="n">
         <v>30.73999977111816</v>
@@ -5467,11 +5479,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>30.4709358215332</v>
+        <v>30.4709415435791</v>
       </c>
       <c r="C195" t="n">
         <v>33.52999877929688</v>
@@ -5492,11 +5504,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>34.53859329223633</v>
+        <v>34.53858947753906</v>
       </c>
       <c r="C196" t="n">
         <v>37.86999893188477</v>
@@ -5517,11 +5529,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>32.48651885986328</v>
+        <v>32.48653411865234</v>
       </c>
       <c r="C197" t="n">
         <v>35.61999893188477</v>
@@ -5542,11 +5554,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>37.04471588134766</v>
+        <v>37.04471206665039</v>
       </c>
       <c r="C198" t="n">
         <v>40.5</v>
@@ -5567,7 +5579,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5592,11 +5604,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>26.80024909973145</v>
+        <v>26.80025291442871</v>
       </c>
       <c r="C200" t="n">
         <v>29.29999923706055</v>
@@ -5617,7 +5629,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5642,7 +5654,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5667,11 +5679,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>33.44654083251953</v>
+        <v>33.44654846191406</v>
       </c>
       <c r="C203" t="n">
         <v>36.41999816894531</v>
@@ -5692,7 +5704,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5717,11 +5729,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>36.25751876831055</v>
+        <v>36.25752258300781</v>
       </c>
       <c r="C205" t="n">
         <v>39.34999847412109</v>
@@ -5742,11 +5754,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>37.98056030273438</v>
+        <v>37.98056411743164</v>
       </c>
       <c r="C206" t="n">
         <v>41.22000122070312</v>
@@ -5767,11 +5779,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>33.52699279785156</v>
+        <v>33.5269889831543</v>
       </c>
       <c r="C207" t="n">
         <v>36.22999954223633</v>
@@ -5796,7 +5808,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5825,11 +5837,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>30.3066291809082</v>
+        <v>30.30662536621094</v>
       </c>
       <c r="C209" t="n">
         <v>32.75</v>
@@ -5854,7 +5866,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -5883,7 +5895,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -5912,11 +5924,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>36.35102081298828</v>
+        <v>36.35102844238281</v>
       </c>
       <c r="C212" t="n">
         <v>39.08000183105469</v>
@@ -5941,11 +5953,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>35.92315292358398</v>
+        <v>35.92314147949219</v>
       </c>
       <c r="C213" t="n">
         <v>38.61999893188477</v>
@@ -5970,11 +5982,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>37.82388305664062</v>
+        <v>37.82387924194336</v>
       </c>
       <c r="C214" t="n">
         <v>40.5</v>
@@ -5999,7 +6011,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6028,11 +6040,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>34.58316040039062</v>
+        <v>34.58316802978516</v>
       </c>
       <c r="C216" t="n">
         <v>37.02999877929688</v>
@@ -6057,7 +6069,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6086,11 +6098,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>33.44162750244141</v>
+        <v>33.44163131713867</v>
       </c>
       <c r="C218" t="n">
         <v>35.65000152587891</v>
@@ -6115,11 +6127,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>32.89756011962891</v>
+        <v>32.89756393432617</v>
       </c>
       <c r="C219" t="n">
         <v>35.06999969482422</v>
@@ -6144,7 +6156,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6173,11 +6185,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>35.31956481933594</v>
+        <v>35.3195686340332</v>
       </c>
       <c r="C221" t="n">
         <v>37.47000122070312</v>
@@ -6202,7 +6214,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6231,11 +6243,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>32.00196075439453</v>
+        <v>32.00195693969727</v>
       </c>
       <c r="C223" t="n">
         <v>33.77999877929688</v>
@@ -6260,11 +6272,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>32.85459518432617</v>
+        <v>32.85459136962891</v>
       </c>
       <c r="C224" t="n">
         <v>34.68000030517578</v>
@@ -6289,11 +6301,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>29.45354843139648</v>
+        <v>29.45355033874512</v>
       </c>
       <c r="C225" t="n">
         <v>31.09000015258789</v>
@@ -6318,11 +6330,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>27.67855834960938</v>
+        <v>27.67856216430664</v>
       </c>
       <c r="C226" t="n">
         <v>29.04999923706055</v>
@@ -6347,11 +6359,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>26.43040657043457</v>
+        <v>26.4304084777832</v>
       </c>
       <c r="C227" t="n">
         <v>27.73999977111816</v>
@@ -6376,7 +6388,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6405,7 +6417,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6434,11 +6446,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>24.92519378662109</v>
+        <v>24.92519187927246</v>
       </c>
       <c r="C230" t="n">
         <v>26.02000045776367</v>
@@ -6463,7 +6475,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6492,11 +6504,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>24.47482872009277</v>
+        <v>24.47482681274414</v>
       </c>
       <c r="C232" t="n">
         <v>25.3700008392334</v>
@@ -6521,7 +6533,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6550,11 +6562,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>18.89877128601074</v>
+        <v>18.89877319335938</v>
       </c>
       <c r="C234" t="n">
         <v>19.59000015258789</v>
@@ -6579,7 +6591,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6608,7 +6620,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6637,7 +6649,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6666,7 +6678,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6695,7 +6707,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6724,7 +6736,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6753,7 +6765,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6782,7 +6794,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6811,7 +6823,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6840,7 +6852,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6869,7 +6881,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6898,7 +6910,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6927,7 +6939,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -6956,7 +6968,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -6985,7 +6997,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7014,32 +7026,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>33.0099983215332</v>
+        <v>32.7599983215332</v>
       </c>
       <c r="C250" t="n">
-        <v>33.0099983215332</v>
+        <v>32.7599983215332</v>
       </c>
       <c r="D250" t="n">
-        <v>171785100</v>
+        <v>179376700</v>
       </c>
       <c r="E250" t="n">
         <v>1.9</v>
       </c>
       <c r="F250" t="n">
-        <v>17.37368332712274</v>
+        <v>17.24210437975432</v>
       </c>
       <c r="G250" t="n">
         <v>833130367</v>
       </c>
       <c r="H250" t="n">
-        <v>27501632016.28834</v>
+        <v>27293349424.53834</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2061923401238836</v>
+        <v>0.2153044794728986</v>
       </c>
     </row>
   </sheetData>
@@ -7071,75 +7083,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40024</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7175,13 +7187,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40109</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7217,13 +7229,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40290</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7259,13 +7271,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40024</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7301,13 +7313,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40109</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7343,13 +7355,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40290</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7385,13 +7397,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40382</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7427,13 +7439,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40473</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7469,13 +7481,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40591</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7502,7 +7514,7 @@
       <c r="I10" t="n">
         <v>2.01</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40591</v>
       </c>
       <c r="K10" t="n">
@@ -7515,13 +7527,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40655</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7548,7 +7560,7 @@
       <c r="I11" t="n">
         <v>2.34</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40655</v>
       </c>
       <c r="K11" t="n">
@@ -7561,13 +7573,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40745</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7594,7 +7606,7 @@
       <c r="I12" t="n">
         <v>2.61</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40745</v>
       </c>
       <c r="K12" t="n">
@@ -7607,13 +7619,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40837</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7640,7 +7652,7 @@
       <c r="I13" t="n">
         <v>2.75</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40837</v>
       </c>
       <c r="K13" t="n">
@@ -7653,13 +7665,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40955</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7686,7 +7698,7 @@
       <c r="I14" t="n">
         <v>3.08</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40955</v>
       </c>
       <c r="K14" t="n">
@@ -7699,13 +7711,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41023</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7732,7 +7744,7 @@
       <c r="I15" t="n">
         <v>3.2</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41023</v>
       </c>
       <c r="K15" t="n">
@@ -7745,13 +7757,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41117</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7778,7 +7790,7 @@
       <c r="I16" t="n">
         <v>3.19</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41117</v>
       </c>
       <c r="K16" t="n">
@@ -7791,13 +7803,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41205</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7824,7 +7836,7 @@
       <c r="I17" t="n">
         <v>3.1</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41205</v>
       </c>
       <c r="K17" t="n">
@@ -7837,13 +7849,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41316</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7870,7 +7882,7 @@
       <c r="I18" t="n">
         <v>2.84</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41316</v>
       </c>
       <c r="K18" t="n">
@@ -7883,13 +7895,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41390</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7916,7 +7928,7 @@
       <c r="I19" t="n">
         <v>2.14</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41390</v>
       </c>
       <c r="K19" t="n">
@@ -7929,13 +7941,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -7962,7 +7974,7 @@
       <c r="I20" t="n">
         <v>2.04</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="K20" t="n">
@@ -7975,13 +7987,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41572</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8008,7 +8020,7 @@
       <c r="I21" t="n">
         <v>2.18</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41572</v>
       </c>
       <c r="K21" t="n">
@@ -8021,13 +8033,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41677</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8054,7 +8066,7 @@
       <c r="I22" t="n">
         <v>2.36</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41677</v>
       </c>
       <c r="K22" t="n">
@@ -8067,13 +8079,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8100,7 +8112,7 @@
       <c r="I23" t="n">
         <v>3.11</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="K23" t="n">
@@ -8113,13 +8125,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8146,7 +8158,7 @@
       <c r="I24" t="n">
         <v>3.33</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="K24" t="n">
@@ -8159,13 +8171,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8192,7 +8204,7 @@
       <c r="I25" t="n">
         <v>3.95</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="K25" t="n">
@@ -8205,13 +8217,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8238,7 +8250,7 @@
       <c r="I26" t="n">
         <v>4.11</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="K26" t="n">
@@ -8251,13 +8263,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8284,7 +8296,7 @@
       <c r="I27" t="n">
         <v>2.620000000000001</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="K27" t="n">
@@ -8297,13 +8309,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42209</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8330,7 +8342,7 @@
       <c r="I28" t="n">
         <v>1.77</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42209</v>
       </c>
       <c r="K28" t="n">
@@ -8343,13 +8355,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8376,7 +8388,7 @@
       <c r="I29" t="n">
         <v>0.3000000000000005</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="K29" t="n">
@@ -8389,13 +8401,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42405</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8422,7 +8434,7 @@
       <c r="I30" t="n">
         <v>-0.79</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42405</v>
       </c>
       <c r="K30" t="n">
@@ -8435,13 +8447,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8468,7 +8480,7 @@
       <c r="I31" t="n">
         <v>-2.84</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="K31" t="n">
@@ -8481,13 +8493,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8523,13 +8535,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42773</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8565,13 +8577,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8607,13 +8619,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8640,7 +8652,7 @@
       <c r="I35" t="n">
         <v>-0.1578530424799087</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="K35" t="n">
@@ -8653,13 +8665,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8686,7 +8698,7 @@
       <c r="I36" t="n">
         <v>0.2521469575200913</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="K36" t="n">
@@ -8699,13 +8711,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43140</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8732,7 +8744,7 @@
       <c r="I37" t="n">
         <v>-0.5349794792615179</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43140</v>
       </c>
       <c r="K37" t="n">
@@ -8745,13 +8757,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8778,7 +8790,7 @@
       <c r="I38" t="n">
         <v>-0.4449794792615179</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="K38" t="n">
@@ -8791,13 +8803,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8824,7 +8836,7 @@
       <c r="I39" t="n">
         <v>0.1028735632183902</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="K39" t="n">
@@ -8837,13 +8849,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8870,7 +8882,7 @@
       <c r="I40" t="n">
         <v>0.1828735632183902</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="K40" t="n">
@@ -8883,13 +8895,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8916,7 +8928,7 @@
       <c r="I41" t="n">
         <v>1.889999999999999</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="K41" t="n">
@@ -8929,13 +8941,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -8962,7 +8974,7 @@
       <c r="I42" t="n">
         <v>2.009999999999999</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="K42" t="n">
@@ -8975,13 +8987,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9008,7 +9020,7 @@
       <c r="I43" t="n">
         <v>1.519999999999999</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="K43" t="n">
@@ -9021,13 +9033,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9054,7 +9066,7 @@
       <c r="I44" t="n">
         <v>1.36</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="K44" t="n">
@@ -9067,13 +9079,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43872</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9100,7 +9112,7 @@
       <c r="I45" t="n">
         <v>-1.289142857142858</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43872</v>
       </c>
       <c r="K45" t="n">
@@ -9113,13 +9125,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43945</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9146,7 +9158,7 @@
       <c r="I46" t="n">
         <v>-2.619142857142857</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43945</v>
       </c>
       <c r="K46" t="n">
@@ -9159,13 +9171,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44036</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9192,7 +9204,7 @@
       <c r="I47" t="n">
         <v>-4.619142857142857</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44036</v>
       </c>
       <c r="K47" t="n">
@@ -9205,13 +9217,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9238,7 +9250,7 @@
       <c r="I48" t="n">
         <v>-4.979142857142857</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="K48" t="n">
@@ -9251,13 +9263,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9284,7 +9296,7 @@
       <c r="I49" t="n">
         <v>-3.34</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="K49" t="n">
@@ -9297,13 +9309,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9330,7 +9342,7 @@
       <c r="I50" t="n">
         <v>-1.990000000000001</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="K50" t="n">
@@ -9343,13 +9355,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44491</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9385,13 +9397,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9427,13 +9439,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44764</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9469,13 +9481,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9511,13 +9523,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44964</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9544,7 +9556,7 @@
       <c r="I55" t="n">
         <v>600001.1336303358</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44964</v>
       </c>
       <c r="K55" t="n">
@@ -9557,13 +9569,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9590,7 +9602,7 @@
       <c r="I56" t="n">
         <v>1320000.842378952</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="K56" t="n">
@@ -9603,13 +9615,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9636,7 +9648,7 @@
       <c r="I57" t="n">
         <v>2000000.72246696</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="K57" t="n">
@@ -9649,13 +9661,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45224</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9682,7 +9694,7 @@
       <c r="I58" t="n">
         <v>2190000.72246696</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45224</v>
       </c>
       <c r="K58" t="n">
@@ -9695,13 +9707,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45328</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9728,7 +9740,7 @@
       <c r="I59" t="n">
         <v>2920000</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45328</v>
       </c>
       <c r="K59" t="n">
@@ -9741,13 +9753,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45406</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9774,7 +9786,7 @@
       <c r="I60" t="n">
         <v>2880000</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45406</v>
       </c>
       <c r="K60" t="n">
@@ -9787,13 +9799,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45502</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9820,7 +9832,7 @@
       <c r="I61" t="n">
         <v>3000000</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45502</v>
       </c>
       <c r="K61" t="n">
@@ -9833,13 +9845,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9866,7 +9878,7 @@
       <c r="I62" t="n">
         <v>2860000</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="K62" t="n">
@@ -9879,13 +9891,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9912,7 +9924,7 @@
       <c r="I63" t="n">
         <v>2830000</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="K63" t="n">
@@ -9925,13 +9937,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -9958,7 +9970,7 @@
       <c r="I64" t="n">
         <v>2150000.24</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="K64" t="n">
@@ -9971,13 +9983,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10004,7 +10016,7 @@
       <c r="I65" t="n">
         <v>1350000.79</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="K65" t="n">
@@ -10017,13 +10029,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10050,7 +10062,7 @@
       <c r="I66" t="n">
         <v>700000.8100000001</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="K66" t="n">
@@ -10063,13 +10075,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10096,7 +10108,7 @@
       <c r="I67" t="n">
         <v>1.5</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="K67" t="n">
@@ -10109,13 +10121,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10142,7 +10154,7 @@
       <c r="I68" t="n">
         <v>1.81</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="K68" t="n">
@@ -10155,13 +10167,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10188,7 +10200,7 @@
       <c r="I69" t="n">
         <v>1.9</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="K69" t="n">
@@ -10225,52 +10237,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40011</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40024</v>
       </c>
       <c r="C2" t="n">
@@ -10299,10 +10311,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40102</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40109</v>
       </c>
       <c r="C3" t="n">
@@ -10331,10 +10343,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40221</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40226</v>
       </c>
       <c r="C4" t="n">
@@ -10363,10 +10375,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40284</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40290</v>
       </c>
       <c r="C5" t="n">
@@ -10395,10 +10407,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40375</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40382</v>
       </c>
       <c r="C6" t="n">
@@ -10427,10 +10439,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40466</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40473</v>
       </c>
       <c r="C7" t="n">
@@ -10459,10 +10471,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40585</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40591</v>
       </c>
       <c r="C8" t="n">
@@ -10491,10 +10503,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40648</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40655</v>
       </c>
       <c r="C9" t="n">
@@ -10523,10 +10535,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40739</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40745</v>
       </c>
       <c r="C10" t="n">
@@ -10555,10 +10567,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40830</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40837</v>
       </c>
       <c r="C11" t="n">
@@ -10587,10 +10599,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40949</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40955</v>
       </c>
       <c r="C12" t="n">
@@ -10619,10 +10631,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41019</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41023</v>
       </c>
       <c r="C13" t="n">
@@ -10651,10 +10663,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41110</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41117</v>
       </c>
       <c r="C14" t="n">
@@ -10683,10 +10695,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41201</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41205</v>
       </c>
       <c r="C15" t="n">
@@ -10715,10 +10727,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41306</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41316</v>
       </c>
       <c r="C16" t="n">
@@ -10747,10 +10759,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41383</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41390</v>
       </c>
       <c r="C17" t="n">
@@ -10779,10 +10791,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41474</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="C18" t="n">
@@ -10811,10 +10823,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41565</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41572</v>
       </c>
       <c r="C19" t="n">
@@ -10843,10 +10855,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41677</v>
       </c>
       <c r="C20" t="n">
@@ -10875,10 +10887,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41747</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="C21" t="n">
@@ -10907,10 +10919,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41838</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="C22" t="n">
@@ -10939,10 +10951,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41929</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="C23" t="n">
@@ -10971,10 +10983,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42052</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="C24" t="n">
@@ -11003,10 +11015,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42111</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="C25" t="n">
@@ -11035,10 +11047,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42202</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42209</v>
       </c>
       <c r="C26" t="n">
@@ -11067,10 +11079,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42293</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="C27" t="n">
@@ -11099,10 +11111,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42398</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42405</v>
       </c>
       <c r="C28" t="n">
@@ -11131,10 +11143,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42489</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="C29" t="n">
@@ -11163,10 +11175,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42576</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="C30" t="n">
@@ -11195,10 +11207,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42664</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="C31" t="n">
@@ -11227,10 +11239,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42773</v>
       </c>
       <c r="C32" t="n">
@@ -11259,10 +11271,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42846</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="C33" t="n">
@@ -11291,10 +11303,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42937</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="C34" t="n">
@@ -11323,10 +11335,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43028</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="C35" t="n">
@@ -11355,10 +11367,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43133</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43140</v>
       </c>
       <c r="C36" t="n">
@@ -11387,10 +11399,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43210</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="C37" t="n">
@@ -11419,10 +11431,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43301</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="C38" t="n">
@@ -11451,10 +11463,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43392</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="C39" t="n">
@@ -11483,10 +11495,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43504</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43509</v>
       </c>
       <c r="C40" t="n">
@@ -11515,10 +11527,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43574</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="C41" t="n">
@@ -11547,10 +11559,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43665</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="C42" t="n">
@@ -11579,10 +11591,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43756</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="C43" t="n">
@@ -11611,10 +11623,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43868</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43872</v>
       </c>
       <c r="C44" t="n">
@@ -11643,10 +11655,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43938</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43945</v>
       </c>
       <c r="C45" t="n">
@@ -11675,10 +11687,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44029</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44036</v>
       </c>
       <c r="C46" t="n">
@@ -11707,10 +11719,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44120</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="C47" t="n">
@@ -11739,10 +11751,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44225</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="C48" t="n">
@@ -11771,10 +11783,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44306</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="C49" t="n">
@@ -11803,10 +11815,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44393</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="C50" t="n">
@@ -11835,10 +11847,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44484</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44491</v>
       </c>
       <c r="C51" t="n">
@@ -11867,10 +11879,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44589</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="C52" t="n">
@@ -11899,10 +11911,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44666</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="C53" t="n">
@@ -11931,10 +11943,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44757</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44764</v>
       </c>
       <c r="C54" t="n">
@@ -11963,10 +11975,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44853</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="C55" t="n">
@@ -11995,10 +12007,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44964</v>
       </c>
       <c r="C56" t="n">
@@ -12027,10 +12039,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45035</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="C57" t="n">
@@ -12059,10 +12071,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45126</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="C58" t="n">
@@ -12091,10 +12103,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45217</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45224</v>
       </c>
       <c r="C59" t="n">
@@ -12123,10 +12135,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45321</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45328</v>
       </c>
       <c r="C60" t="n">
@@ -12155,10 +12167,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45399</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45406</v>
       </c>
       <c r="C61" t="n">
@@ -12187,10 +12199,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45495</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45502</v>
       </c>
       <c r="C62" t="n">
@@ -12219,10 +12231,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="C63" t="n">
@@ -12251,10 +12263,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45693</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="C64" t="n">
@@ -12283,10 +12295,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45765</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="C65" t="n">
@@ -12315,10 +12327,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45856</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="C66" t="n">
@@ -12347,10 +12359,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45947</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="C67" t="n">
@@ -12379,10 +12391,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46052</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="C68" t="n">
@@ -12411,10 +12423,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="C69" t="n">
@@ -12443,10 +12455,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46220</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="C70" t="n">
@@ -12493,12 +12505,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/HAL.xlsx
+++ b/salidas/empresas/HAL.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>28.74216651916504</v>
+        <v>28.74217796325684</v>
       </c>
       <c r="C2" t="n">
         <v>39.81000137329102</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>24.60093307495117</v>
+        <v>24.60092163085938</v>
       </c>
       <c r="C3" t="n">
         <v>34</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>26.41704750061035</v>
+        <v>26.41705894470215</v>
       </c>
       <c r="C4" t="n">
         <v>36.5099983215332</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>28.27297592163086</v>
+        <v>28.27298355102539</v>
       </c>
       <c r="C5" t="n">
         <v>39.07500076293945</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>27.04010963439941</v>
+        <v>27.04011726379395</v>
       </c>
       <c r="C6" t="n">
         <v>37.29499816894531</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>24.18711471557617</v>
+        <v>24.18711853027344</v>
       </c>
       <c r="C8" t="n">
         <v>33.36000061035156</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>23.70346450805664</v>
+        <v>23.70346069335938</v>
       </c>
       <c r="C9" t="n">
         <v>32.61999893188477</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>20.67331504821777</v>
+        <v>20.67331123352051</v>
       </c>
       <c r="C10" t="n">
         <v>28.45000076293945</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>23.50727081298828</v>
+        <v>23.50727272033691</v>
       </c>
       <c r="C11" t="n">
         <v>32.34999847412109</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>24.57365226745605</v>
+        <v>24.57365417480469</v>
       </c>
       <c r="C12" t="n">
         <v>33.7400016784668</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>22.61446571350098</v>
+        <v>22.61447334289551</v>
       </c>
       <c r="C13" t="n">
         <v>31.04999923706055</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>21.51469993591309</v>
+        <v>21.51469421386719</v>
       </c>
       <c r="C14" t="n">
         <v>29.54000091552734</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>22.57285690307617</v>
+        <v>22.57286071777344</v>
       </c>
       <c r="C15" t="n">
         <v>30.92000007629395</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>23.17149925231934</v>
+        <v>23.17148971557617</v>
       </c>
       <c r="C16" t="n">
         <v>31.73999977111816</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>23.19339561462402</v>
+        <v>23.19338989257812</v>
       </c>
       <c r="C17" t="n">
         <v>31.77000045776367</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>26.31112098693848</v>
+        <v>26.31112670898438</v>
       </c>
       <c r="C18" t="n">
         <v>35.95000076293945</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>25.24989318847656</v>
+        <v>25.24990272521973</v>
       </c>
       <c r="C19" t="n">
         <v>34.5</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>25.38510894775391</v>
+        <v>25.38510513305664</v>
       </c>
       <c r="C21" t="n">
         <v>34.59000015258789</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>28.18121337890625</v>
+        <v>28.18120384216309</v>
       </c>
       <c r="C22" t="n">
         <v>38.40000152587891</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>28.92977905273438</v>
+        <v>28.92976188659668</v>
       </c>
       <c r="C23" t="n">
         <v>39.41999816894531</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>27.89163017272949</v>
+        <v>27.8916187286377</v>
       </c>
       <c r="C25" t="n">
         <v>37.90999984741211</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>28.24626922607422</v>
+        <v>28.24627304077148</v>
       </c>
       <c r="C27" t="n">
         <v>38.29999923706055</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>29.00589942932129</v>
+        <v>29.00588989257812</v>
       </c>
       <c r="C28" t="n">
         <v>39.33000183105469</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>33.8586311340332</v>
+        <v>33.85863494873047</v>
       </c>
       <c r="C29" t="n">
         <v>45.90999984741211</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>39.2112922668457</v>
+        <v>39.2113037109375</v>
       </c>
       <c r="C31" t="n">
         <v>53.06999969482422</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>33.11572265625</v>
+        <v>33.1157112121582</v>
       </c>
       <c r="C32" t="n">
         <v>44.81999969482422</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>32.52947616577148</v>
+        <v>32.52949523925781</v>
       </c>
       <c r="C33" t="n">
         <v>43.93999862670898</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>23.97883224487305</v>
+        <v>23.97882843017578</v>
       </c>
       <c r="C34" t="n">
         <v>32.38999938964844</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>14.65085411071777</v>
+        <v>14.65085506439209</v>
       </c>
       <c r="C35" t="n">
         <v>19.79000091552734</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>13.02956008911133</v>
+        <v>13.02955627441406</v>
       </c>
       <c r="C36" t="n">
         <v>17.60000038146973</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>13.52812004089355</v>
+        <v>13.52811813354492</v>
       </c>
       <c r="C37" t="n">
         <v>18.18000030517578</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>12.83608436584473</v>
+        <v>12.83609199523926</v>
       </c>
       <c r="C38" t="n">
         <v>17.25</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>12.2023754119873</v>
+        <v>12.20237255096436</v>
       </c>
       <c r="C39" t="n">
         <v>16.30999946594238</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>11.57392501831055</v>
+        <v>11.5739278793335</v>
       </c>
       <c r="C40" t="n">
         <v>15.47000026702881</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>15.12765979766846</v>
+        <v>15.12765121459961</v>
       </c>
       <c r="C41" t="n">
         <v>20.21999931335449</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>17.22541999816895</v>
+        <v>17.22542381286621</v>
       </c>
       <c r="C42" t="n">
         <v>22.93000030517578</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>15.55020618438721</v>
+        <v>15.55020999908447</v>
       </c>
       <c r="C43" t="n">
         <v>20.70000076293945</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>16.59440040588379</v>
+        <v>16.59439849853516</v>
       </c>
       <c r="C44" t="n">
         <v>22.09000015258789</v>
@@ -1321,7 +1321,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>17.87805938720703</v>
+        <v>17.87804985046387</v>
       </c>
       <c r="C45" t="n">
         <v>23.70999908447266</v>
@@ -1346,7 +1346,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>20.44930267333984</v>
+        <v>20.44929122924805</v>
       </c>
       <c r="C46" t="n">
         <v>27.1200008392334</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>22.02522087097168</v>
+        <v>22.02522468566895</v>
       </c>
       <c r="C47" t="n">
         <v>29.20999908447266</v>
@@ -1396,7 +1396,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>22.13833045959473</v>
+        <v>22.13832855224609</v>
       </c>
       <c r="C48" t="n">
         <v>29.36000061035156</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>22.75853538513184</v>
+        <v>22.75852584838867</v>
       </c>
       <c r="C49" t="n">
         <v>30.09000015258789</v>
@@ -1446,7 +1446,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>22.09294509887695</v>
+        <v>22.09294128417969</v>
       </c>
       <c r="C50" t="n">
         <v>29.20999908447266</v>
@@ -1471,7 +1471,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>22.87252807617188</v>
+        <v>22.87252998352051</v>
       </c>
       <c r="C51" t="n">
         <v>30.14999961853027</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>23.25183486938477</v>
+        <v>23.2518367767334</v>
       </c>
       <c r="C53" t="n">
         <v>30.64999961853027</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>18.90238189697266</v>
+        <v>18.90238571166992</v>
       </c>
       <c r="C54" t="n">
         <v>24.82999992370605</v>
@@ -1621,7 +1621,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>21.54176330566406</v>
+        <v>21.54176139831543</v>
       </c>
       <c r="C57" t="n">
         <v>28.20999908447266</v>
@@ -1646,7 +1646,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>25.25296401977539</v>
+        <v>25.25296783447266</v>
       </c>
       <c r="C58" t="n">
         <v>33.06999969482422</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>24.3289909362793</v>
+        <v>24.3289852142334</v>
       </c>
       <c r="C59" t="n">
         <v>31.86000061035156</v>
@@ -1696,7 +1696,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>28.89544105529785</v>
+        <v>28.89545440673828</v>
       </c>
       <c r="C60" t="n">
         <v>37.84000015258789</v>
@@ -1721,7 +1721,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>31.25300407409668</v>
+        <v>31.25299453735352</v>
       </c>
       <c r="C61" t="n">
         <v>40.83000183105469</v>
@@ -1746,7 +1746,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>34.44490814208984</v>
+        <v>34.44490432739258</v>
       </c>
       <c r="C62" t="n">
         <v>45</v>
@@ -1829,7 +1829,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>38.7136116027832</v>
+        <v>38.71360778808594</v>
       </c>
       <c r="C65" t="n">
         <v>50.47999954223633</v>
@@ -1858,7 +1858,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>38.52896499633789</v>
+        <v>38.52898406982422</v>
       </c>
       <c r="C66" t="n">
         <v>50.15000152587891</v>
@@ -1887,7 +1887,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>39.1820068359375</v>
+        <v>39.18200302124023</v>
       </c>
       <c r="C67" t="n">
         <v>51</v>
@@ -1916,7 +1916,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>42.04766845703125</v>
+        <v>42.04767227172852</v>
       </c>
       <c r="C68" t="n">
         <v>54.72999954223633</v>
@@ -1945,7 +1945,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>34.16017150878906</v>
+        <v>34.16016387939453</v>
       </c>
       <c r="C69" t="n">
         <v>44.36999893188477</v>
@@ -2032,7 +2032,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>28.40809059143066</v>
+        <v>28.4080982208252</v>
       </c>
       <c r="C72" t="n">
         <v>36.79999923706055</v>
@@ -2061,7 +2061,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>26.64030265808105</v>
+        <v>26.64029884338379</v>
       </c>
       <c r="C73" t="n">
         <v>34.5099983215332</v>
@@ -2090,7 +2090,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>28.39265823364258</v>
+        <v>28.39265251159668</v>
       </c>
       <c r="C74" t="n">
         <v>36.77999877929688</v>
@@ -2119,7 +2119,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>28.24599266052246</v>
+        <v>28.24598693847656</v>
       </c>
       <c r="C75" t="n">
         <v>36.59000015258789</v>
@@ -2148,7 +2148,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>25.6854419708252</v>
+        <v>25.68544960021973</v>
       </c>
       <c r="C76" t="n">
         <v>33.18999862670898</v>
@@ -2177,7 +2177,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>26.48255729675293</v>
+        <v>26.4825611114502</v>
       </c>
       <c r="C77" t="n">
         <v>34.22000122070312</v>
@@ -2206,7 +2206,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>23.26317024230957</v>
+        <v>23.2631664276123</v>
       </c>
       <c r="C78" t="n">
         <v>30.05999946594238</v>
@@ -2235,7 +2235,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>22.03695487976074</v>
+        <v>22.03694915771484</v>
       </c>
       <c r="C79" t="n">
         <v>28.38999938964844</v>
@@ -2264,7 +2264,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>25.71624374389648</v>
+        <v>25.71623992919922</v>
       </c>
       <c r="C80" t="n">
         <v>33.13000106811523</v>
@@ -2293,7 +2293,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>25.49897384643555</v>
+        <v>25.49896812438965</v>
       </c>
       <c r="C81" t="n">
         <v>32.7599983215332</v>
@@ -2322,7 +2322,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>26.22286415100098</v>
+        <v>26.22285461425781</v>
       </c>
       <c r="C82" t="n">
         <v>33.68999862670898</v>
@@ -2351,7 +2351,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>25.13315582275391</v>
+        <v>25.13315773010254</v>
       </c>
       <c r="C83" t="n">
         <v>32.29000091552734</v>
@@ -2380,7 +2380,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>25.95820999145508</v>
+        <v>25.95821952819824</v>
       </c>
       <c r="C84" t="n">
         <v>33.34999847412109</v>
@@ -2409,7 +2409,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>27.07487106323242</v>
+        <v>27.07487869262695</v>
       </c>
       <c r="C85" t="n">
         <v>34.68999862670898</v>
@@ -2438,7 +2438,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>31.74995994567871</v>
+        <v>31.74994659423828</v>
       </c>
       <c r="C86" t="n">
         <v>40.68000030517578</v>
@@ -2467,7 +2467,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>32.39775085449219</v>
+        <v>32.39775466918945</v>
       </c>
       <c r="C87" t="n">
         <v>41.5099983215332</v>
@@ -2496,7 +2496,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>31.63654327392578</v>
+        <v>31.63655853271484</v>
       </c>
       <c r="C88" t="n">
         <v>40.40999984741211</v>
@@ -2525,7 +2525,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>33.48416900634766</v>
+        <v>33.48418045043945</v>
       </c>
       <c r="C89" t="n">
         <v>42.77000045776367</v>
@@ -2554,7 +2554,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>32.76390838623047</v>
+        <v>32.76391220092773</v>
       </c>
       <c r="C90" t="n">
         <v>41.84999847412109</v>
@@ -2583,7 +2583,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>32.7599983215332</v>
+        <v>32.75999450683594</v>
       </c>
       <c r="C91" t="n">
         <v>41.72000122070312</v>
@@ -2612,7 +2612,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>35.48475646972656</v>
+        <v>35.48476028442383</v>
       </c>
       <c r="C92" t="n">
         <v>45.18999862670898</v>
@@ -2641,7 +2641,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>37.78858947753906</v>
+        <v>37.78856658935547</v>
       </c>
       <c r="C93" t="n">
         <v>48</v>
@@ -2670,7 +2670,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>37.90668106079102</v>
+        <v>37.90666580200195</v>
       </c>
       <c r="C94" t="n">
         <v>48.15000152587891</v>
@@ -2699,7 +2699,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>41.74850463867188</v>
+        <v>41.74849319458008</v>
       </c>
       <c r="C95" t="n">
         <v>53.02999877929688</v>
@@ -2728,7 +2728,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>41.47296142578125</v>
+        <v>41.47295761108398</v>
       </c>
       <c r="C96" t="n">
         <v>52.68000030517578</v>
@@ -2786,7 +2786,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>38.69528198242188</v>
+        <v>38.69528961181641</v>
       </c>
       <c r="C98" t="n">
         <v>49.0099983215332</v>
@@ -2815,7 +2815,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>45.00370788574219</v>
+        <v>45.00370407104492</v>
       </c>
       <c r="C99" t="n">
         <v>57</v>
@@ -2844,7 +2844,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>46.61861801147461</v>
+        <v>46.61862564086914</v>
       </c>
       <c r="C100" t="n">
         <v>58.88999938964844</v>
@@ -2902,7 +2902,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>51.17043685913086</v>
+        <v>51.17044067382812</v>
       </c>
       <c r="C102" t="n">
         <v>64.63999938964844</v>
@@ -2931,7 +2931,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>56.34381484985352</v>
+        <v>56.34382247924805</v>
       </c>
       <c r="C103" t="n">
         <v>71.01000213623047</v>
@@ -2960,7 +2960,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>54.74101638793945</v>
+        <v>54.74102401733398</v>
       </c>
       <c r="C104" t="n">
         <v>68.98999786376953</v>
@@ -3018,7 +3018,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>51.30051803588867</v>
+        <v>51.30051422119141</v>
       </c>
       <c r="C106" t="n">
         <v>64.51000213623047</v>
@@ -3047,7 +3047,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>43.84918212890625</v>
+        <v>43.84916305541992</v>
       </c>
       <c r="C107" t="n">
         <v>55.13999938964844</v>
@@ -3105,7 +3105,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>31.41671943664551</v>
+        <v>31.41671752929688</v>
       </c>
       <c r="C109" t="n">
         <v>39.33000183105469</v>
@@ -3134,7 +3134,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>31.94391441345215</v>
+        <v>31.94392585754395</v>
       </c>
       <c r="C110" t="n">
         <v>39.9900016784668</v>
@@ -3192,7 +3192,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>35.19879531860352</v>
+        <v>35.19879150390625</v>
       </c>
       <c r="C112" t="n">
         <v>43.88000106811523</v>
@@ -3221,7 +3221,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>39.26573944091797</v>
+        <v>39.26574325561523</v>
       </c>
       <c r="C113" t="n">
         <v>48.95000076293945</v>
@@ -3250,7 +3250,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>36.41808700561523</v>
+        <v>36.4180793762207</v>
       </c>
       <c r="C114" t="n">
         <v>45.40000152587891</v>
@@ -3279,7 +3279,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>34.68656921386719</v>
+        <v>34.68657302856445</v>
       </c>
       <c r="C115" t="n">
         <v>43.06999969482422</v>
@@ -3308,7 +3308,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>33.65571594238281</v>
+        <v>33.65572357177734</v>
       </c>
       <c r="C116" t="n">
         <v>41.79000091552734</v>
@@ -3337,7 +3337,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>31.83915710449219</v>
+        <v>31.83915901184082</v>
       </c>
       <c r="C117" t="n">
         <v>39.34999847412109</v>
@@ -3366,7 +3366,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>28.6026668548584</v>
+        <v>28.60266304016113</v>
       </c>
       <c r="C118" t="n">
         <v>35.34999847412109</v>
@@ -3395,7 +3395,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>31.05432319641113</v>
+        <v>31.0543098449707</v>
       </c>
       <c r="C119" t="n">
         <v>38.38000106811523</v>
@@ -3424,7 +3424,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>32.24372482299805</v>
+        <v>32.24374771118164</v>
       </c>
       <c r="C120" t="n">
         <v>39.84999847412109</v>
@@ -3453,7 +3453,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>27.66767120361328</v>
+        <v>27.66768074035645</v>
       </c>
       <c r="C121" t="n">
         <v>34.04000091552734</v>
@@ -3482,7 +3482,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>25.8388786315918</v>
+        <v>25.83887481689453</v>
       </c>
       <c r="C122" t="n">
         <v>31.79000091552734</v>
@@ -3511,7 +3511,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>26.38188552856445</v>
+        <v>26.38188743591309</v>
       </c>
       <c r="C123" t="n">
         <v>32.27999877929688</v>
@@ -3565,7 +3565,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>33.76196670532227</v>
+        <v>33.7619514465332</v>
       </c>
       <c r="C125" t="n">
         <v>41.31000137329102</v>
@@ -3592,7 +3592,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>34.61912155151367</v>
+        <v>34.61911392211914</v>
       </c>
       <c r="C126" t="n">
         <v>42.18000030517578</v>
@@ -3619,7 +3619,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>37.17164611816406</v>
+        <v>37.1716423034668</v>
       </c>
       <c r="C127" t="n">
         <v>45.29000091552734</v>
@@ -3646,7 +3646,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>35.83383178710938</v>
+        <v>35.83383560180664</v>
       </c>
       <c r="C128" t="n">
         <v>43.65999984741211</v>
@@ -3673,7 +3673,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>35.30033493041992</v>
+        <v>35.30034255981445</v>
       </c>
       <c r="C129" t="n">
         <v>43.0099983215332</v>
@@ -3700,7 +3700,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>36.98921585083008</v>
+        <v>36.98923873901367</v>
       </c>
       <c r="C130" t="n">
         <v>44.88000106811523</v>
@@ -3727,7 +3727,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>37.91230773925781</v>
+        <v>37.91231536865234</v>
       </c>
       <c r="C131" t="n">
         <v>46</v>
@@ -3754,7 +3754,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>43.75575256347656</v>
+        <v>43.75574111938477</v>
       </c>
       <c r="C132" t="n">
         <v>53.09000015258789</v>
@@ -3781,7 +3781,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>44.72855377197266</v>
+        <v>44.72855758666992</v>
       </c>
       <c r="C133" t="n">
         <v>54.09000015258789</v>
@@ -3806,7 +3806,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>46.77933502197266</v>
+        <v>46.77934265136719</v>
       </c>
       <c r="C134" t="n">
         <v>56.56999969482422</v>
@@ -3831,7 +3831,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>44.35861587524414</v>
+        <v>44.35861206054688</v>
       </c>
       <c r="C135" t="n">
         <v>53.45999908447266</v>
@@ -3856,7 +3856,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>40.8321533203125</v>
+        <v>40.8321647644043</v>
       </c>
       <c r="C136" t="n">
         <v>49.20999908447266</v>
@@ -3881,7 +3881,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>38.0690803527832</v>
+        <v>38.06908416748047</v>
       </c>
       <c r="C137" t="n">
         <v>45.88000106811523</v>
@@ -3906,7 +3906,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>37.49655151367188</v>
+        <v>37.49655532836914</v>
       </c>
       <c r="C138" t="n">
         <v>45.18999862670898</v>
@@ -3931,7 +3931,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>35.58013534545898</v>
+        <v>35.58013916015625</v>
       </c>
       <c r="C139" t="n">
         <v>42.70999908447266</v>
@@ -4010,7 +4010,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>38.52386093139648</v>
+        <v>38.52385330200195</v>
       </c>
       <c r="C142" t="n">
         <v>46.02999877929688</v>
@@ -4037,7 +4037,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>35.77035522460938</v>
+        <v>35.77035903930664</v>
       </c>
       <c r="C143" t="n">
         <v>42.7400016784668</v>
@@ -4066,7 +4066,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>34.96690368652344</v>
+        <v>34.96689605712891</v>
       </c>
       <c r="C144" t="n">
         <v>41.77999877929688</v>
@@ -4095,7 +4095,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>41.07016754150391</v>
+        <v>41.07016372680664</v>
       </c>
       <c r="C145" t="n">
         <v>48.86999893188477</v>
@@ -4153,7 +4153,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>39.01119613647461</v>
+        <v>39.01119995117188</v>
       </c>
       <c r="C147" t="n">
         <v>46.41999816894531</v>
@@ -4207,7 +4207,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>44.70656967163086</v>
+        <v>44.70656204223633</v>
       </c>
       <c r="C149" t="n">
         <v>52.9900016784668</v>
@@ -4234,7 +4234,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>41.964599609375</v>
+        <v>41.9646110534668</v>
       </c>
       <c r="C150" t="n">
         <v>49.7400016784668</v>
@@ -4261,7 +4261,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>38.1594352722168</v>
+        <v>38.15942001342773</v>
       </c>
       <c r="C151" t="n">
         <v>45.06000137329102</v>
@@ -4317,7 +4317,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>33.78116607666016</v>
+        <v>33.78116989135742</v>
       </c>
       <c r="C153" t="n">
         <v>39.88999938964844</v>
@@ -4346,7 +4346,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>34.47874069213867</v>
+        <v>34.47873687744141</v>
       </c>
       <c r="C154" t="n">
         <v>40.52999877929688</v>
@@ -4375,7 +4375,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>29.50217819213867</v>
+        <v>29.50216674804688</v>
       </c>
       <c r="C155" t="n">
         <v>34.68000030517578</v>
@@ -4404,7 +4404,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>26.73740386962891</v>
+        <v>26.73740577697754</v>
       </c>
       <c r="C156" t="n">
         <v>31.43000030517578</v>
@@ -4462,7 +4462,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>26.83147811889648</v>
+        <v>26.83147048950195</v>
       </c>
       <c r="C158" t="n">
         <v>31.36000061035156</v>
@@ -4491,7 +4491,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>26.25822448730469</v>
+        <v>26.25822257995605</v>
       </c>
       <c r="C159" t="n">
         <v>30.69000053405762</v>
@@ -4520,7 +4520,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>25.21544647216797</v>
+        <v>25.21545028686523</v>
       </c>
       <c r="C160" t="n">
         <v>29.29999923706055</v>
@@ -4549,7 +4549,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>24.38066673278809</v>
+        <v>24.38066864013672</v>
       </c>
       <c r="C161" t="n">
         <v>28.32999992370605</v>
@@ -4578,7 +4578,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>18.32207870483398</v>
+        <v>18.32208061218262</v>
       </c>
       <c r="C162" t="n">
         <v>21.29000091552734</v>
@@ -4607,7 +4607,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>19.7343921661377</v>
+        <v>19.73439407348633</v>
       </c>
       <c r="C163" t="n">
         <v>22.73999977111816</v>
@@ -4636,7 +4636,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>19.96002578735352</v>
+        <v>19.96003150939941</v>
       </c>
       <c r="C164" t="n">
         <v>23</v>
@@ -4665,7 +4665,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>16.3498649597168</v>
+        <v>16.34987449645996</v>
       </c>
       <c r="C165" t="n">
         <v>18.84000015258789</v>
@@ -4694,7 +4694,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>16.51634407043457</v>
+        <v>16.5163516998291</v>
       </c>
       <c r="C166" t="n">
         <v>18.85000038146973</v>
@@ -4723,7 +4723,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>16.86682891845703</v>
+        <v>16.8668270111084</v>
       </c>
       <c r="C167" t="n">
         <v>19.25</v>
@@ -4752,7 +4752,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>18.39141464233398</v>
+        <v>18.39140892028809</v>
       </c>
       <c r="C168" t="n">
         <v>20.98999977111816</v>
@@ -4781,7 +4781,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>21.62783813476562</v>
+        <v>21.62783432006836</v>
       </c>
       <c r="C169" t="n">
         <v>24.46999931335449</v>
@@ -4810,7 +4810,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>19.27679443359375</v>
+        <v>19.27679634094238</v>
       </c>
       <c r="C170" t="n">
         <v>21.80999946594238</v>
@@ -4866,7 +4866,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>6.118336200714111</v>
+        <v>6.118335723876953</v>
       </c>
       <c r="C172" t="n">
         <v>6.849999904632568</v>
@@ -4893,7 +4893,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>9.378471374511719</v>
+        <v>9.378467559814453</v>
       </c>
       <c r="C173" t="n">
         <v>10.5</v>
@@ -4920,7 +4920,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>10.49495124816895</v>
+        <v>10.49495601654053</v>
       </c>
       <c r="C174" t="n">
         <v>11.75</v>
@@ -4947,7 +4947,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>11.63706970214844</v>
+        <v>11.63706874847412</v>
       </c>
       <c r="C175" t="n">
         <v>12.97999954223633</v>
@@ -5001,7 +5001,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>14.50599098205566</v>
+        <v>14.50599193572998</v>
       </c>
       <c r="C177" t="n">
         <v>16.18000030517578</v>
@@ -5028,7 +5028,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>10.833420753479</v>
+        <v>10.83341884613037</v>
       </c>
       <c r="C178" t="n">
         <v>12.05000019073486</v>
@@ -5055,7 +5055,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>10.8424129486084</v>
+        <v>10.84241104125977</v>
       </c>
       <c r="C179" t="n">
         <v>12.0600004196167</v>
@@ -5082,7 +5082,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>14.91505908966064</v>
+        <v>14.9150562286377</v>
       </c>
       <c r="C180" t="n">
         <v>16.59000015258789</v>
@@ -5109,7 +5109,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>17.0367259979248</v>
+        <v>17.03672218322754</v>
       </c>
       <c r="C181" t="n">
         <v>18.89999961853027</v>
@@ -5190,7 +5190,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>19.38224601745605</v>
+        <v>19.38224792480469</v>
       </c>
       <c r="C184" t="n">
         <v>21.45999908447266</v>
@@ -5217,7 +5217,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>17.66620445251465</v>
+        <v>17.66620254516602</v>
       </c>
       <c r="C185" t="n">
         <v>19.55999946594238</v>
@@ -5244,7 +5244,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>20.27639389038086</v>
+        <v>20.27639579772949</v>
       </c>
       <c r="C186" t="n">
         <v>22.45000076293945</v>
@@ -5271,7 +5271,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>20.92346954345703</v>
+        <v>20.92346382141113</v>
       </c>
       <c r="C187" t="n">
         <v>23.1200008392334</v>
@@ -5298,7 +5298,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>18.71527862548828</v>
+        <v>18.71528244018555</v>
       </c>
       <c r="C188" t="n">
         <v>20.68000030517578</v>
@@ -5352,7 +5352,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>19.6097469329834</v>
+        <v>19.60974502563477</v>
       </c>
       <c r="C190" t="n">
         <v>21.6200008392334</v>
@@ -5406,7 +5406,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>19.58253479003906</v>
+        <v>19.5825309753418</v>
       </c>
       <c r="C192" t="n">
         <v>21.59000015258789</v>
@@ -5433,7 +5433,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>20.78348731994629</v>
+        <v>20.78349304199219</v>
       </c>
       <c r="C193" t="n">
         <v>22.8700008392334</v>
@@ -5483,7 +5483,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>30.4709415435791</v>
+        <v>30.47093963623047</v>
       </c>
       <c r="C195" t="n">
         <v>33.52999877929688</v>
@@ -5508,7 +5508,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>34.53858947753906</v>
+        <v>34.53859710693359</v>
       </c>
       <c r="C196" t="n">
         <v>37.86999893188477</v>
@@ -5583,7 +5583,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>28.68450164794922</v>
+        <v>28.68450355529785</v>
       </c>
       <c r="C199" t="n">
         <v>31.36000061035156</v>
@@ -5608,7 +5608,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>26.80025291442871</v>
+        <v>26.80025100708008</v>
       </c>
       <c r="C200" t="n">
         <v>29.29999923706055</v>
@@ -5633,7 +5633,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>27.5594367980957</v>
+        <v>27.55944061279297</v>
       </c>
       <c r="C201" t="n">
         <v>30.1299991607666</v>
@@ -5658,7 +5658,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>22.60993766784668</v>
+        <v>22.60993576049805</v>
       </c>
       <c r="C202" t="n">
         <v>24.6200008392334</v>
@@ -5708,7 +5708,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>34.79653167724609</v>
+        <v>34.7965202331543</v>
       </c>
       <c r="C204" t="n">
         <v>37.88999938964844</v>
@@ -5733,7 +5733,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>36.25752258300781</v>
+        <v>36.25751876831055</v>
       </c>
       <c r="C205" t="n">
         <v>39.34999847412109</v>
@@ -5758,7 +5758,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>37.98056411743164</v>
+        <v>37.98055648803711</v>
       </c>
       <c r="C206" t="n">
         <v>41.22000122070312</v>
@@ -5783,7 +5783,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>33.5269889831543</v>
+        <v>33.52699661254883</v>
       </c>
       <c r="C207" t="n">
         <v>36.22999954223633</v>
@@ -5812,7 +5812,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>29.27944183349609</v>
+        <v>29.27943801879883</v>
       </c>
       <c r="C208" t="n">
         <v>31.63999938964844</v>
@@ -5841,7 +5841,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>30.30662536621094</v>
+        <v>30.3066234588623</v>
       </c>
       <c r="C209" t="n">
         <v>32.75</v>
@@ -5870,7 +5870,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>26.51251602172852</v>
+        <v>26.51251411437988</v>
       </c>
       <c r="C210" t="n">
         <v>28.64999961853027</v>
@@ -5899,7 +5899,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>30.68628883361816</v>
+        <v>30.6862907409668</v>
       </c>
       <c r="C211" t="n">
         <v>32.9900016784668</v>
@@ -5928,7 +5928,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>36.35102844238281</v>
+        <v>36.35102462768555</v>
       </c>
       <c r="C212" t="n">
         <v>39.08000183105469</v>
@@ -6015,7 +6015,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>36.74052047729492</v>
+        <v>36.74052810668945</v>
       </c>
       <c r="C215" t="n">
         <v>39.34000015258789</v>
@@ -6044,7 +6044,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>34.58316802978516</v>
+        <v>34.58317184448242</v>
       </c>
       <c r="C216" t="n">
         <v>37.02999877929688</v>
@@ -6073,7 +6073,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>33.91066360473633</v>
+        <v>33.91065979003906</v>
       </c>
       <c r="C217" t="n">
         <v>36.15000152587891</v>
@@ -6102,7 +6102,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>33.44163131713867</v>
+        <v>33.44163513183594</v>
       </c>
       <c r="C218" t="n">
         <v>35.65000152587891</v>
@@ -6131,7 +6131,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>32.89756393432617</v>
+        <v>32.89756011962891</v>
       </c>
       <c r="C219" t="n">
         <v>35.06999969482422</v>
@@ -6160,7 +6160,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>37.15764999389648</v>
+        <v>37.15765380859375</v>
       </c>
       <c r="C220" t="n">
         <v>39.41999816894531</v>
@@ -6189,7 +6189,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>35.3195686340332</v>
+        <v>35.31956100463867</v>
       </c>
       <c r="C221" t="n">
         <v>37.47000122070312</v>
@@ -6276,7 +6276,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>32.85459136962891</v>
+        <v>32.85458755493164</v>
       </c>
       <c r="C224" t="n">
         <v>34.68000030517578</v>
@@ -6363,7 +6363,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>26.4304084777832</v>
+        <v>26.43040657043457</v>
       </c>
       <c r="C227" t="n">
         <v>27.73999977111816</v>
@@ -6392,7 +6392,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>30.35590362548828</v>
+        <v>30.35590553283691</v>
       </c>
       <c r="C228" t="n">
         <v>31.86000061035156</v>
@@ -6479,7 +6479,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>25.26046562194824</v>
+        <v>25.26046371459961</v>
       </c>
       <c r="C231" t="n">
         <v>26.3700008392334</v>
@@ -6566,7 +6566,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>18.89877319335938</v>
+        <v>18.89876937866211</v>
       </c>
       <c r="C234" t="n">
         <v>19.59000015258789</v>
@@ -6653,7 +6653,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>22.11197090148926</v>
+        <v>22.11197280883789</v>
       </c>
       <c r="C237" t="n">
         <v>22.72999954223633</v>
@@ -6711,7 +6711,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>26.30732536315918</v>
+        <v>26.30732727050781</v>
       </c>
       <c r="C239" t="n">
         <v>26.84000015258789</v>
@@ -6740,7 +6740,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>25.69962882995605</v>
+        <v>25.69963073730469</v>
       </c>
       <c r="C240" t="n">
         <v>26.21999931335449</v>
@@ -6769,7 +6769,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>27.875244140625</v>
+        <v>27.87524223327637</v>
       </c>
       <c r="C241" t="n">
         <v>28.26000022888184</v>
@@ -6798,7 +6798,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>33.06363296508789</v>
+        <v>33.06362915039062</v>
       </c>
       <c r="C242" t="n">
         <v>33.52000045776367</v>
@@ -6827,7 +6827,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>35.50986480712891</v>
+        <v>35.50986862182617</v>
       </c>
       <c r="C243" t="n">
         <v>36</v>
